--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.91569500091143</v>
+        <v>2.261300437648108</v>
       </c>
       <c r="D2" t="n">
-        <v>12.57180565831166</v>
+        <v>2.042918419475644</v>
       </c>
       <c r="E2" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F2" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.71619572990855</v>
+        <v>0.2788818061101394</v>
       </c>
       <c r="D3" t="n">
-        <v>2.49890001665989</v>
+        <v>0.4060712527072322</v>
       </c>
       <c r="E3" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F3" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.82746877835745</v>
+        <v>1.759463676483085</v>
       </c>
       <c r="D4" t="n">
-        <v>10.78668203706</v>
+        <v>1.75283583102225</v>
       </c>
       <c r="E4" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F4" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.96959336097057</v>
+        <v>1.457558921157718</v>
       </c>
       <c r="D5" t="n">
-        <v>9.375752146148178</v>
+        <v>1.523559723749079</v>
       </c>
       <c r="E5" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F5" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.43202647945547</v>
+        <v>2.182704302911513</v>
       </c>
       <c r="D6" t="n">
-        <v>6.391466103199009</v>
+        <v>1.038613241769839</v>
       </c>
       <c r="E6" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F6" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.86682734571967</v>
+        <v>6.315859443679447</v>
       </c>
       <c r="D7" t="n">
-        <v>39.12043839843471</v>
+        <v>6.357071239745641</v>
       </c>
       <c r="E7" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F7" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.46543636978184</v>
+        <v>4.625633410089549</v>
       </c>
       <c r="D8" t="n">
-        <v>30.44149407756464</v>
+        <v>4.946742787604255</v>
       </c>
       <c r="E8" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F8" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.16751981590457</v>
+        <v>1.652221970084493</v>
       </c>
       <c r="D9" t="n">
-        <v>8.12409163710284</v>
+        <v>1.320164891029211</v>
       </c>
       <c r="E9" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F9" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.28495729244766</v>
+        <v>3.783805560022744</v>
       </c>
       <c r="D10" t="n">
-        <v>27.16818189836487</v>
+        <v>4.414829558484291</v>
       </c>
       <c r="E10" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F10" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.11353751081675</v>
+        <v>1.643449845507722</v>
       </c>
       <c r="D11" t="n">
-        <v>8.455668354821954</v>
+        <v>1.374046107658568</v>
       </c>
       <c r="E11" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F11" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70125052297407</v>
+        <v>2.713953209983286</v>
       </c>
       <c r="D12" t="n">
-        <v>20.89146791817993</v>
+        <v>3.394863536704238</v>
       </c>
       <c r="E12" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F12" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>4.553843884696843</v>
+        <v>0.7399996312632371</v>
       </c>
       <c r="D13" t="n">
-        <v>12.04072006667532</v>
+        <v>1.95661701083474</v>
       </c>
       <c r="E13" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F13" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>10.16089838937991</v>
+        <v>1.651145988274235</v>
       </c>
       <c r="D14" t="n">
-        <v>5.946815276205093</v>
+        <v>0.9663574823833277</v>
       </c>
       <c r="E14" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F14" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.5897283739109</v>
+        <v>5.783330860760522</v>
       </c>
       <c r="D15" t="n">
-        <v>38.37782257190326</v>
+        <v>6.23639616793428</v>
       </c>
       <c r="E15" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F15" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>12.64911064067352</v>
+        <v>2.055480479109447</v>
       </c>
       <c r="D16" t="n">
-        <v>2.895063345143793</v>
+        <v>0.4704477935858665</v>
       </c>
       <c r="E16" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F16" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.42663604829041</v>
+        <v>5.431828357847192</v>
       </c>
       <c r="D17" t="n">
-        <v>35.17799081559694</v>
+        <v>5.716423507534503</v>
       </c>
       <c r="E17" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F17" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>24.47092723762754</v>
+        <v>3.976525676114475</v>
       </c>
       <c r="D18" t="n">
-        <v>13.79231983358559</v>
+        <v>2.241251972957659</v>
       </c>
       <c r="E18" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F18" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>27.5</v>
+        <v>4.46875</v>
       </c>
       <c r="D19" t="n">
-        <v>18.86286993966268</v>
+        <v>3.065216365195186</v>
       </c>
       <c r="E19" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F19" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>26.16457352346126</v>
+        <v>4.251743197562456</v>
       </c>
       <c r="D20" t="n">
-        <v>23.3514354118737</v>
+        <v>3.794608254429477</v>
       </c>
       <c r="E20" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F20" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>21.61376189637599</v>
+        <v>3.512236308161098</v>
       </c>
       <c r="D21" t="n">
-        <v>21.19746126016113</v>
+        <v>3.444587454776185</v>
       </c>
       <c r="E21" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F21" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>23.08730265332076</v>
+        <v>3.751686681164624</v>
       </c>
       <c r="D22" t="n">
-        <v>31.18641472880031</v>
+        <v>5.06779239343005</v>
       </c>
       <c r="E22" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F22" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>17.68954273846175</v>
+        <v>2.874550695000034</v>
       </c>
       <c r="D23" t="n">
-        <v>16.91401909512087</v>
+        <v>2.748528102957141</v>
       </c>
       <c r="E23" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F23" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>11.40518569651903</v>
+        <v>1.853342675684343</v>
       </c>
       <c r="D24" t="n">
-        <v>41.65449187862064</v>
+        <v>6.768854930275854</v>
       </c>
       <c r="E24" t="n">
-        <v>9.842992061315671</v>
+        <v>1.599486209963797</v>
       </c>
       <c r="F24" t="n">
-        <v>11.97928073687654</v>
+        <v>1.946633119742437</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
